--- a/wiki/reports/daily/2026-10-21_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-21_일일보고.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,13 +75,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +91,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -184,25 +184,31 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,13 +220,19 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -605,14 +617,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>재연마 일일생산 보고  ─  2026년 10월 21일  (2026-10-21 08:02 생성 · 속보값)</t>
+          <t>재연마 일일생산 보고  ─  2026년 10월 21일  (2026-10-21 16:00 생성 · 속보값)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-21 08:02   |   전일: 10월 20일   |   월평균 기준: 이전 작업일 12일 평균   |   10월 누적 작업일: 13일</t>
+          <t>생성: 2026-10-21 16:00   |   전일: 10월 20일   |   월평균 기준: 이전 작업일 12일 평균   |   10월 누적 작업일: 13일</t>
         </is>
       </c>
     </row>
@@ -674,27 +686,27 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>15</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-10</v>
+        <v>17</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.6666666666666666</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>43.4</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>-38.41666666666666</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>-0.8848368522072937</v>
-      </c>
-      <c r="I4" s="10" t="inlineStr"/>
+      <c r="G4" s="10" t="n">
+        <v>-11.41666666666666</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>-0.2629558541266794</v>
+      </c>
+      <c r="I4" s="12" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -703,205 +715,205 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1950</v>
+        <v>7618</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>3870</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-1920</v>
+        <v>3748</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.4961240310077519</v>
+        <v>0.9684754521963824</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>9829.9</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>-7879.916666666666</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>-0.8016259886909859</v>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>0:32:30</t>
+      <c r="G5" s="10" t="n">
+        <v>-2211.916666666666</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>-0.225018862486118</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>2:06:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>GX7  수량 (개)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>8</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-1</v>
+        <v>0.625</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>28.3</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>-28.33333333333333</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="n">
+        <v>-15.33333333333333</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>-0.5411764705882353</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>GX7  가공시간 (초)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0</v>
+        <v>3053</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1892</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-1892</v>
+        <v>1161</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-1</v>
+        <v>0.6136363636363636</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>9145.200000000001</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>-9145.166666666666</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>0:00:00</t>
+      <c r="G7" s="10" t="n">
+        <v>-6092.166666666666</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>-0.6661624537551712</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>0:50:53</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>합계  수량 (개)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>23</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-18</v>
+        <v>22</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.7826086956521739</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>71.8</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>-66.75</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>-0.9303135888501742</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr"/>
+      <c r="G8" s="10" t="n">
+        <v>-26.75</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>-0.3728222996515679</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>합계  가공시간 (초)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1950</v>
+        <v>10671</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>5762</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-3812</v>
+        <v>4909</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.6615758417216244</v>
+        <v>0.8519611246095106</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>18975.1</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>-17025.08333333333</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>-0.8972336529044668</v>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>0:32:30</t>
+      <c r="G9" s="10" t="n">
+        <v>-8304.083333333332</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>-0.4376309282787515</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>2:57:51</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>합계  금액</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>23</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-18</v>
+        <v>22</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.7826086956521739</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>71.8</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>-66.75</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>-0.9303135888501742</v>
-      </c>
-      <c r="I10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="n">
+        <v>-26.75</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>-0.3728222996515679</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>10월 누적  (13일 / 21일 중 작업일)</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n">
-        <v>866</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>229651</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>866</v>
-      </c>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="16" t="n">
+        <v>906</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>238372</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>906</v>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -919,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -943,213 +955,641 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>■ FAST GRIND</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>면취</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>0030</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr"/>
-      <c r="I4" s="19" t="n">
+      <c r="H4" s="19" t="inlineStr"/>
+      <c r="I4" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="21" t="n">
         <v>1950</v>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>0:32:30</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>0178</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr"/>
+      <c r="I5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>310</v>
+      </c>
+      <c r="K5" s="19" t="inlineStr">
+        <is>
+          <t>0:05:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>0088</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr"/>
+      <c r="I6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>225</v>
+      </c>
+      <c r="K6" s="19" t="inlineStr">
+        <is>
+          <t>0:03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>R0.3</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>0088</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr"/>
+      <c r="I7" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>2585</v>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>0:43:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>0088</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
+        <is>
+          <t>0:23:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>0088</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>350</v>
+      </c>
+      <c r="K9" s="19" t="inlineStr">
+        <is>
+          <t>0:05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>0088</t>
+        </is>
+      </c>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>344</v>
+      </c>
+      <c r="K10" s="19" t="inlineStr">
+        <is>
+          <t>0:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>0085</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>454</v>
+      </c>
+      <c r="K11" s="19" t="inlineStr">
+        <is>
+          <t>0:07:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>FAST GRIND 소계</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>1950</v>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>0:32:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>7618</v>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>2:06:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>■ GX7</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="K15" s="23" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>(해당일 작업 없음)</t>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>0177</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr"/>
+      <c r="I16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>230</v>
+      </c>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>0:03:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr"/>
+      <c r="I17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>690</v>
+      </c>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>0:11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G18" s="25" t="inlineStr">
+        <is>
+          <t>0177</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr"/>
+      <c r="I18" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>2133</v>
+      </c>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>0:35:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>GX7 소계</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="J19" s="16" t="n">
+        <v>3053</v>
+      </c>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>0:50:53</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
